--- a/business_forms/043_retail_sustainability_score_program_application--business_forms.xlsx
+++ b/business_forms/043_retail_sustainability_score_program_application--business_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -748,12 +748,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'reduce_waste_and_pollution'}</t>
+          <t>reduce_waste_and_pollution</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Reduce waste and pollution'}</t>
+          <t>Reduce waste and pollution</t>
         </is>
       </c>
     </row>
@@ -765,12 +765,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'source_materials_sustainably'}</t>
+          <t>source_materials_sustainably</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Source materials sustainably'}</t>
+          <t>Source materials sustainably</t>
         </is>
       </c>
     </row>
@@ -782,12 +782,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'improve_supply_chain_management'}</t>
+          <t>improve_supply_chain_management</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Improve supply chain management'}</t>
+          <t>Improve supply chain management</t>
         </is>
       </c>
     </row>
@@ -799,12 +799,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'support_biodiversity_conservation'}</t>
+          <t>support_biodiversity_conservation</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Support biodiversity conservation'}</t>
+          <t>Support biodiversity conservation</t>
         </is>
       </c>
     </row>
@@ -816,12 +816,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'engage_customers_and_educate'}</t>
+          <t>engage_customers_and_educate</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Engage customers and educate'}</t>
+          <t>Engage customers and educate</t>
         </is>
       </c>
     </row>
@@ -833,12 +833,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'improve_supply_chain_transparency_and_accountability'}</t>
+          <t>improve_supply_chain_transparency_and_accountability</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Improve supply chain transparency and accountability'}</t>
+          <t>Improve supply chain transparency and accountability</t>
         </is>
       </c>
     </row>
@@ -850,12 +850,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'manage_chemical_use'}</t>
+          <t>manage_chemical_use</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Manage chemical use'}</t>
+          <t>Manage chemical use</t>
         </is>
       </c>
     </row>
@@ -867,12 +867,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'improve_water_management'}</t>
+          <t>improve_water_management</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Improve water management'}</t>
+          <t>Improve water management</t>
         </is>
       </c>
     </row>
@@ -884,12 +884,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'engage_with_local_communities'}</t>
+          <t>engage_with_local_communities</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Engage with local communities'}</t>
+          <t>Engage with local communities</t>
         </is>
       </c>
     </row>
@@ -901,12 +901,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'improve_employee_engagement'}</t>
+          <t>improve_employee_engagement</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Improve employee engagement'}</t>
+          <t>Improve employee engagement</t>
         </is>
       </c>
     </row>
@@ -918,12 +918,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'energy_and_climate'}</t>
+          <t>energy_and_climate</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Energy and Climate'}</t>
+          <t>Energy and Climate</t>
         </is>
       </c>
     </row>
@@ -935,12 +935,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'water_and_waste'}</t>
+          <t>water_and_waste</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Water and Waste'}</t>
+          <t>Water and Waste</t>
         </is>
       </c>
     </row>
@@ -952,12 +952,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'supply_chain'}</t>
+          <t>supply_chain</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Supply Chain'}</t>
+          <t>Supply Chain</t>
         </is>
       </c>
     </row>
@@ -969,12 +969,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'product_and_packaging'}</t>
+          <t>product_and_packaging</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Product and Packaging'}</t>
+          <t>Product and Packaging</t>
         </is>
       </c>
     </row>
@@ -986,12 +986,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'human_rights_and_labor'}</t>
+          <t>human_rights_and_labor</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Human Rights and Labor'}</t>
+          <t>Human Rights and Labor</t>
         </is>
       </c>
     </row>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'biodiversity_and_ecosystems'}</t>
+          <t>biodiversity_and_ecosystems</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Biodiversity and Ecosystems'}</t>
+          <t>Biodiversity and Ecosystems</t>
         </is>
       </c>
     </row>
@@ -1020,12 +1020,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'community_and_social'}</t>
+          <t>community_and_social</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Community and Social'}</t>
+          <t>Community and Social</t>
         </is>
       </c>
     </row>
@@ -1037,12 +1037,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'resource_efficiency'}</t>
+          <t>resource_efficiency</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Resource Efficiency'}</t>
+          <t>Resource Efficiency</t>
         </is>
       </c>
     </row>
